--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:48</t>
+    <t xml:space="preserve">2026-09-10 00:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:57</t>
+    <t xml:space="preserve">2026-09-18 11:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:05</t>
+    <t xml:space="preserve">2026-09-23 14:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:28</t>
+    <t xml:space="preserve">2026-10-02 15:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2023_biobio.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Cañete</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Concepción</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Quilleco</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Coronel</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:35</t>
+    <t xml:space="preserve">2026-10-04 10:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:13</t>
+    <t xml:space="preserve">2026-10-05 14:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
